--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CACERES PATRIMONIO DE LA HUMANIDAD.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CACERES PATRIMONIO DE LA HUMANIDAD.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>105.4602</v>
+        <v>75.523</v>
       </c>
       <c r="E2" t="n">
-        <v>102.1895</v>
+        <v>80.6604</v>
       </c>
       <c r="F2" t="n">
-        <v>3.271100000000001</v>
+        <v>-5.137700000000001</v>
       </c>
       <c r="G2" t="n">
         <v>28.0227</v>
@@ -610,13 +610,13 @@
         <v>40.1669</v>
       </c>
       <c r="S2" t="n">
-        <v>46.6103</v>
+        <v>16.6726</v>
       </c>
       <c r="T2" t="n">
-        <v>31.5211</v>
+        <v>9.992000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>15.0895</v>
+        <v>6.6807</v>
       </c>
       <c r="V2" t="n">
         <v>40.8175</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>30.0696</v>
+        <v>33.6639</v>
       </c>
       <c r="E3" t="n">
-        <v>39.6812</v>
+        <v>24.8227</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.6111</v>
+        <v>8.841399999999998</v>
       </c>
       <c r="G3" t="n">
-        <v>22.838</v>
+        <v>5.283999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>17.8812</v>
+        <v>-3.6417</v>
       </c>
       <c r="I3" t="n">
-        <v>4.956800000000001</v>
+        <v>8.925800000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>52.6406</v>
+        <v>28.6042</v>
       </c>
       <c r="K3" t="n">
-        <v>29.5922</v>
+        <v>6.8368</v>
       </c>
       <c r="L3" t="n">
-        <v>23.0483</v>
+        <v>21.7677</v>
       </c>
       <c r="M3" t="n">
-        <v>-29.8026</v>
+        <v>-23.32</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.711</v>
+        <v>-10.4782</v>
       </c>
       <c r="O3" t="n">
-        <v>-18.0916</v>
+        <v>-12.8419</v>
       </c>
       <c r="P3" t="n">
-        <v>-6.243399999999999</v>
+        <v>18.1063</v>
       </c>
       <c r="Q3" t="n">
-        <v>-44.5375</v>
+        <v>-24.5581</v>
       </c>
       <c r="R3" t="n">
-        <v>38.2938</v>
+        <v>42.6644</v>
       </c>
       <c r="S3" t="n">
-        <v>11.4305</v>
+        <v>1.3438</v>
       </c>
       <c r="T3" t="n">
-        <v>9.1119</v>
+        <v>-0.3271999999999998</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3183</v>
+        <v>1.6714</v>
       </c>
       <c r="V3" t="n">
-        <v>2.044799999999999</v>
+        <v>8.93</v>
       </c>
       <c r="W3" t="n">
-        <v>22.4661</v>
+        <v>21.104</v>
       </c>
       <c r="X3" t="n">
-        <v>-20.4212</v>
+        <v>-12.1739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>18.1125</v>
+        <v>24.687</v>
       </c>
       <c r="E4" t="n">
-        <v>13.4734</v>
+        <v>34.9988</v>
       </c>
       <c r="F4" t="n">
-        <v>4.638999999999999</v>
+        <v>-10.3121</v>
       </c>
       <c r="G4" t="n">
-        <v>5.283999999999999</v>
+        <v>22.838</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.6417</v>
+        <v>17.8812</v>
       </c>
       <c r="I4" t="n">
-        <v>8.925800000000001</v>
+        <v>4.956800000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>28.6042</v>
+        <v>52.6406</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8368</v>
+        <v>29.5922</v>
       </c>
       <c r="L4" t="n">
-        <v>21.7677</v>
+        <v>23.0483</v>
       </c>
       <c r="M4" t="n">
-        <v>-23.32</v>
+        <v>-29.8026</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.4782</v>
+        <v>-11.711</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.8419</v>
+        <v>-18.0916</v>
       </c>
       <c r="P4" t="n">
-        <v>18.1063</v>
+        <v>-6.243399999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-24.5581</v>
+        <v>-44.5375</v>
       </c>
       <c r="R4" t="n">
-        <v>42.6644</v>
+        <v>38.2938</v>
       </c>
       <c r="S4" t="n">
-        <v>-14.2076</v>
+        <v>6.0474</v>
       </c>
       <c r="T4" t="n">
-        <v>-11.6767</v>
+        <v>4.4298</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.5309</v>
+        <v>1.6177</v>
       </c>
       <c r="V4" t="n">
-        <v>8.93</v>
+        <v>2.044799999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>21.104</v>
+        <v>22.4661</v>
       </c>
       <c r="X4" t="n">
-        <v>-12.1739</v>
+        <v>-20.4212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>15.2017</v>
+        <v>21.5112</v>
       </c>
       <c r="E5" t="n">
-        <v>7.2151</v>
+        <v>24.1313</v>
       </c>
       <c r="F5" t="n">
-        <v>7.986499999999999</v>
+        <v>-2.620099999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>15.1124</v>
+        <v>49.5045</v>
       </c>
       <c r="H5" t="n">
-        <v>15.2594</v>
+        <v>17.2816</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1469000000000003</v>
+        <v>32.2235</v>
       </c>
       <c r="J5" t="n">
-        <v>12.5266</v>
+        <v>76.41759999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9308</v>
+        <v>28.8295</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4042</v>
+        <v>47.5879</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5857</v>
+        <v>-26.9128</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3287</v>
+        <v>-11.5478</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2573</v>
+        <v>-15.3645</v>
       </c>
       <c r="P5" t="n">
-        <v>3.538</v>
+        <v>-33.299</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.6141</v>
+        <v>-76.17149999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>14.152</v>
+        <v>42.8724</v>
       </c>
       <c r="S5" t="n">
-        <v>6.927999999999999</v>
+        <v>-5.3408</v>
       </c>
       <c r="T5" t="n">
-        <v>5.0195</v>
+        <v>-4.6838</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9083</v>
+        <v>-0.6565000000000002</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.3769</v>
+        <v>10.6456</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2831000000000001</v>
+        <v>28.5688</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.6598</v>
+        <v>-17.9232</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. KALINICENKO</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>8.138</v>
+        <v>10.854</v>
       </c>
       <c r="E6" t="n">
-        <v>7.0913</v>
+        <v>2.6306</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0468</v>
+        <v>8.2232</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3251000000000002</v>
+        <v>15.1124</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5036</v>
+        <v>15.2594</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8286000000000002</v>
+        <v>-0.1469000000000003</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2756000000000003</v>
+        <v>12.5266</v>
       </c>
       <c r="K6" t="n">
-        <v>1.541</v>
+        <v>13.9308</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2655</v>
+        <v>-1.4042</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6006</v>
+        <v>2.5857</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0374</v>
+        <v>1.3287</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4368</v>
+        <v>1.2573</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1218</v>
+        <v>3.538</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2487</v>
+        <v>-10.6141</v>
       </c>
       <c r="R6" t="n">
-        <v>4.3705</v>
+        <v>14.152</v>
       </c>
       <c r="S6" t="n">
-        <v>3.0062</v>
+        <v>2.5804</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9343</v>
+        <v>0.4353</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07189999999999996</v>
+        <v>2.1452</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3351</v>
+        <v>-10.3769</v>
       </c>
       <c r="W6" t="n">
-        <v>5.130100000000001</v>
+        <v>0.2831000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.795</v>
+        <v>-10.6598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>L. PAUL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>5.7053</v>
+        <v>7.663399999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0611</v>
+        <v>16.3699</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6443</v>
+        <v>-8.7064</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5118</v>
+        <v>25.7461</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4892</v>
+        <v>6.767299999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.977300000000001</v>
+        <v>18.9787</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9291</v>
+        <v>37.6405</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4982</v>
+        <v>13.6982</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5691999999999999</v>
+        <v>23.9424</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4174</v>
+        <v>-11.8944</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.009099999999999997</v>
+        <v>-6.930800000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4084</v>
+        <v>-4.9637</v>
       </c>
       <c r="P7" t="n">
-        <v>6.0354</v>
+        <v>-19.1467</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2487</v>
+        <v>-40.167</v>
       </c>
       <c r="R7" t="n">
-        <v>7.2841</v>
+        <v>21.02</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.6013</v>
+        <v>0.6611</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.0605</v>
+        <v>-0.06680000000000008</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.5407</v>
+        <v>0.7282000000000002</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2406000000000001</v>
+        <v>0.4032</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4412</v>
+        <v>18.9634</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6818</v>
+        <v>-18.5601</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. PAUL</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>5.2247</v>
+        <v>7.0454</v>
       </c>
       <c r="E8" t="n">
-        <v>16.6634</v>
+        <v>4.62</v>
       </c>
       <c r="F8" t="n">
-        <v>-11.4387</v>
+        <v>2.4252</v>
       </c>
       <c r="G8" t="n">
-        <v>25.7461</v>
+        <v>3.5118</v>
       </c>
       <c r="H8" t="n">
-        <v>6.767299999999999</v>
+        <v>5.4892</v>
       </c>
       <c r="I8" t="n">
-        <v>18.9787</v>
+        <v>-1.977300000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>37.6405</v>
+        <v>4.9291</v>
       </c>
       <c r="K8" t="n">
-        <v>13.6982</v>
+        <v>5.4982</v>
       </c>
       <c r="L8" t="n">
-        <v>23.9424</v>
+        <v>-0.5691999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-11.8944</v>
+        <v>-1.4174</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.930800000000001</v>
+        <v>-0.009099999999999997</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.9637</v>
+        <v>-1.4084</v>
       </c>
       <c r="P8" t="n">
-        <v>-19.1467</v>
+        <v>6.0354</v>
       </c>
       <c r="Q8" t="n">
-        <v>-40.167</v>
+        <v>-1.2487</v>
       </c>
       <c r="R8" t="n">
-        <v>21.02</v>
+        <v>7.2841</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.778</v>
+        <v>-2.2612</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2262999999999999</v>
+        <v>-1.5014</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.0043</v>
+        <v>-0.7598</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4032</v>
+        <v>-0.2406000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>18.9634</v>
+        <v>2.4412</v>
       </c>
       <c r="X8" t="n">
-        <v>-18.5601</v>
+        <v>-2.6818</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>E. KALINICENKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4.532999999999999</v>
+        <v>6.455500000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>11.8174</v>
+        <v>5.1857</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.284600000000001</v>
+        <v>1.27</v>
       </c>
       <c r="G9" t="n">
-        <v>49.5045</v>
+        <v>-0.3251000000000002</v>
       </c>
       <c r="H9" t="n">
-        <v>17.2816</v>
+        <v>0.5036</v>
       </c>
       <c r="I9" t="n">
-        <v>32.2235</v>
+        <v>-0.8286000000000002</v>
       </c>
       <c r="J9" t="n">
-        <v>76.41759999999999</v>
+        <v>0.2756000000000003</v>
       </c>
       <c r="K9" t="n">
-        <v>28.8295</v>
+        <v>1.541</v>
       </c>
       <c r="L9" t="n">
-        <v>47.5879</v>
+        <v>-1.2655</v>
       </c>
       <c r="M9" t="n">
-        <v>-26.9128</v>
+        <v>-0.6006</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.5478</v>
+        <v>-1.0374</v>
       </c>
       <c r="O9" t="n">
-        <v>-15.3645</v>
+        <v>0.4368</v>
       </c>
       <c r="P9" t="n">
-        <v>-33.299</v>
+        <v>3.1218</v>
       </c>
       <c r="Q9" t="n">
-        <v>-76.17149999999999</v>
+        <v>-1.2487</v>
       </c>
       <c r="R9" t="n">
-        <v>42.8724</v>
+        <v>4.3705</v>
       </c>
       <c r="S9" t="n">
-        <v>-22.3183</v>
+        <v>1.3239</v>
       </c>
       <c r="T9" t="n">
-        <v>-16.998</v>
+        <v>1.0289</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.3206</v>
+        <v>0.2951</v>
       </c>
       <c r="V9" t="n">
-        <v>10.6456</v>
+        <v>2.3351</v>
       </c>
       <c r="W9" t="n">
-        <v>28.5688</v>
+        <v>5.130100000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-17.9232</v>
+        <v>-2.795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>N. MARINA PARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>4.0968</v>
+        <v>3.3995</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6689</v>
+        <v>-1.451</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5721000000000002</v>
+        <v>4.8504</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.126</v>
+        <v>6.2412</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2171000000000001</v>
+        <v>1.2794</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3431</v>
+        <v>4.961399999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8343</v>
+        <v>6.7568</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4423</v>
+        <v>1.7465</v>
       </c>
       <c r="L10" t="n">
-        <v>0.392</v>
+        <v>5.0103</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.96</v>
+        <v>-0.5156999999999997</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2252</v>
+        <v>-0.4667999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.735</v>
+        <v>-0.04900000000000015</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7054</v>
+        <v>-5.202999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2893</v>
+        <v>-12.4872</v>
       </c>
       <c r="R10" t="n">
-        <v>4.9948</v>
+        <v>7.2841</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7474</v>
+        <v>0.2387</v>
       </c>
       <c r="T10" t="n">
-        <v>3.496799999999999</v>
+        <v>0.5472</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7496</v>
+        <v>-0.3083</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2298999999999999</v>
+        <v>2.1228</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6275</v>
+        <v>3.7325</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8574</v>
+        <v>-1.6098</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RUIZ CRESPO</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3053</v>
+        <v>1.4376</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2.0132</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3053</v>
+        <v>-0.5760999999999998</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2857</v>
+        <v>-1.126</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1429</v>
+        <v>0.2171000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1429</v>
+        <v>-1.3431</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.8343</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1.4423</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.392</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2857</v>
+        <v>-2.96</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1429</v>
+        <v>-1.2252</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1429</v>
+        <v>-1.735</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.7054</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.9948</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0196</v>
+        <v>0.08779999999999991</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.8412000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0196</v>
+        <v>-0.7533999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.2298999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8574</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. LÓPEZ YUSTE</t>
+          <t>J. RUIZ CRESPO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1621</v>
+        <v>0.3347</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0461</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2081</v>
+        <v>0.3347</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0192</v>
+        <v>0.2857</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0192</v>
+        <v>0.1429</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0192</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0192</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.2857</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0489</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.0489</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. MARINA PARRA</t>
+          <t>J. LÓPEZ YUSTE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03710000000000058</v>
+        <v>0.2692</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.617299999999999</v>
+        <v>0.0611</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6546</v>
+        <v>0.2081</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2412</v>
+        <v>0.0192</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2794</v>
+        <v>0.0192</v>
       </c>
       <c r="I13" t="n">
-        <v>4.961399999999999</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>6.7568</v>
+        <v>0.0192</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7465</v>
+        <v>0.0192</v>
       </c>
       <c r="L13" t="n">
-        <v>5.0103</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5156999999999997</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4667999999999999</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.04900000000000015</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.202999999999999</v>
+        <v>0.2081</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.4872</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>7.2841</v>
+        <v>0.2081</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.1236</v>
+        <v>0.0419</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6194</v>
+        <v>0.0419</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5042</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1228</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7325</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5881</v>
+        <v>-0.5294</v>
       </c>
       <c r="E14" t="n">
         <v>-0.1374</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4508</v>
+        <v>-0.392</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2886</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2995</v>
+        <v>-0.2407</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.2501</v>
+        <v>-2.1136</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.7878</v>
+        <v>-1.6807</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4621</v>
+        <v>-0.4328</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0209</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1885</v>
+        <v>-0.05189999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1304</v>
+        <v>-0.02329999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.05810000000000001</v>
+        <v>-0.0287</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>-7.926600000000001</v>
+        <v>-6.0093</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.9967</v>
+        <v>-14.0385</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0702</v>
+        <v>8.029299999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-3.4088</v>
@@ -1702,13 +1702,13 @@
         <v>8.3248</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.7888</v>
+        <v>-0.8718999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1166</v>
+        <v>-1.1585</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.6725</v>
+        <v>0.2865999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-3.6017</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FOREMAN JR</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-8.281799999999999</v>
+        <v>-6.823900000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.3109</v>
+        <v>-10.5045</v>
       </c>
       <c r="F17" t="n">
-        <v>4.029199999999999</v>
+        <v>3.6806</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2174000000000001</v>
+        <v>-8.7646</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4845</v>
+        <v>-4.4222</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2672</v>
+        <v>-4.3424</v>
       </c>
       <c r="J17" t="n">
-        <v>5.224399999999999</v>
+        <v>1.934300000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>6.5198</v>
+        <v>3.4972</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2958</v>
+        <v>-1.5629</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.0067</v>
+        <v>-10.6987</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.0353</v>
+        <v>-7.9192</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02850000000000002</v>
+        <v>-2.7797</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.908499999999999</v>
+        <v>5.827</v>
       </c>
       <c r="Q17" t="n">
-        <v>-19.5632</v>
+        <v>-18.9388</v>
       </c>
       <c r="R17" t="n">
-        <v>11.6547</v>
+        <v>24.766</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6924</v>
+        <v>-3.8901</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4360000000000001</v>
+        <v>-4.2021</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2565</v>
+        <v>0.3123</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.2834</v>
+        <v>0.003599999999999604</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5921</v>
+        <v>10.7022</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.8754</v>
+        <v>-10.6989</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>D. FOREMAN JR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>-12.3733</v>
+        <v>-9.924899999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.4566</v>
+        <v>-13.1867</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0836</v>
+        <v>3.2617</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.7646</v>
+        <v>0.2174000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.4222</v>
+        <v>1.4845</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.3424</v>
+        <v>-1.2672</v>
       </c>
       <c r="J18" t="n">
-        <v>1.934300000000001</v>
+        <v>5.224399999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4972</v>
+        <v>6.5198</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5629</v>
+        <v>-1.2958</v>
       </c>
       <c r="M18" t="n">
-        <v>-10.6987</v>
+        <v>-5.0067</v>
       </c>
       <c r="N18" t="n">
-        <v>-7.9192</v>
+        <v>-5.0353</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.7797</v>
+        <v>0.02850000000000002</v>
       </c>
       <c r="P18" t="n">
-        <v>5.827</v>
+        <v>-7.908499999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-18.9388</v>
+        <v>-19.5632</v>
       </c>
       <c r="R18" t="n">
-        <v>24.766</v>
+        <v>11.6547</v>
       </c>
       <c r="S18" t="n">
-        <v>-9.439399999999999</v>
+        <v>1.0495</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.1547</v>
+        <v>-0.4396999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2848000000000001</v>
+        <v>1.4892</v>
       </c>
       <c r="V18" t="n">
-        <v>0.003599999999999604</v>
+        <v>-3.2834</v>
       </c>
       <c r="W18" t="n">
-        <v>10.7022</v>
+        <v>1.5921</v>
       </c>
       <c r="X18" t="n">
-        <v>-10.6989</v>
+        <v>-4.8754</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-36.9063</v>
+        <v>-17.7869</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.871</v>
+        <v>-2.639999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-24.0351</v>
+        <v>-15.1473</v>
       </c>
       <c r="G19" t="n">
         <v>3.1095</v>
@@ -1936,13 +1936,13 @@
         <v>34.7557</v>
       </c>
       <c r="S19" t="n">
-        <v>-28.7385</v>
+        <v>-9.6191</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.853</v>
+        <v>-3.6217</v>
       </c>
       <c r="U19" t="n">
-        <v>-14.8857</v>
+        <v>-5.9973</v>
       </c>
       <c r="V19" t="n">
         <v>-14.1909</v>
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>128.7200999999999</v>
+        <v>149.6564</v>
       </c>
       <c r="E20" t="n">
-        <v>146.6375</v>
+        <v>151.8549</v>
       </c>
       <c r="F20" t="n">
-        <v>-17.9158</v>
+        <v>-2.199900000000003</v>
       </c>
       <c r="G20" t="n">
         <v>144.9585</v>
@@ -1984,7 +1984,7 @@
         <v>90.35899999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>54.59890000000001</v>
+        <v>54.5989</v>
       </c>
       <c r="J20" t="n">
         <v>304.8658</v>
@@ -2011,16 +2011,16 @@
         <v>-341.3154</v>
       </c>
       <c r="R20" t="n">
-        <v>302.8123</v>
+        <v>302.8122999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-13.1143</v>
+        <v>7.8203</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.124300000000005</v>
+        <v>1.096100000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.990999999999996</v>
+        <v>6.726300000000001</v>
       </c>
       <c r="V20" t="n">
         <v>35.3792</v>
